--- a/Catch models/quantis_msy_conjunto_dbsra.xlsx
+++ b/Catch models/quantis_msy_conjunto_dbsra.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1616.257154854631</v>
+        <v>1711.183010367147</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1913.083358443768</v>
+        <v>1973.7883300746</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>2049.797304225833</v>
+        <v>2086.605564234411</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2251.401057249952</v>
+        <v>2286.487003249185</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3756.723389290012</v>
+        <v>3997.403697729087</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/quantis_msy_conjunto_dbsra.xlsx
+++ b/Catch models/quantis_msy_conjunto_dbsra.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1711.183010367147</v>
+        <v>1100.247101965883</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1973.7883300746</v>
+        <v>1287.507214764437</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>2086.605564234411</v>
+        <v>1362.058002362462</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2286.487003249185</v>
+        <v>1424.664999101444</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3997.403697729087</v>
+        <v>3028.019539421519</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/quantis_msy_conjunto_dbsra.xlsx
+++ b/Catch models/quantis_msy_conjunto_dbsra.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1100.247101965883</v>
+        <v>1465.900445349769</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1287.507214764437</v>
+        <v>1696.692791060076</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>1362.058002362462</v>
+        <v>1842.210690476626</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1424.664999101444</v>
+        <v>1921.503538722845</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3028.019539421519</v>
+        <v>3759.405316433127</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/quantis_msy_conjunto_dbsra.xlsx
+++ b/Catch models/quantis_msy_conjunto_dbsra.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1465.900445349769</v>
+        <v>1547.590983763033</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1696.692791060076</v>
+        <v>1769.905068207934</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>1842.210690476626</v>
+        <v>1880.736666135308</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1921.503538722845</v>
+        <v>1958.706982403877</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3759.405316433127</v>
+        <v>3821.819252485621</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/quantis_msy_conjunto_dbsra.xlsx
+++ b/Catch models/quantis_msy_conjunto_dbsra.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1547.590983763033</v>
+        <v>1556.567709589955</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1769.905068207934</v>
+        <v>1786.028316787664</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>1880.736666135308</v>
+        <v>1892.898478314209</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1958.706982403877</v>
+        <v>1974.08319608134</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3821.819252485621</v>
+        <v>3749.93361100175</v>
       </c>
     </row>
   </sheetData>
